--- a/slide_classification/TCGA_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -514,10 +514,10 @@
         <v>2.5e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.554013</v>
+        <v>0.448974</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.58682</v>
+        <v>0.877519</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.474976</v>
+        <v>0.24653</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -643,10 +643,10 @@
         <v>0.013965</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.493267</v>
+        <v>0.703529</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4591</v>
+        <v>0.34309</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -729,10 +729,10 @@
         <v>0.808652</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.498925</v>
+        <v>0.559322</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.475462</v>
+        <v>0.493473</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.490426</v>
+        <v>0.281568</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>0.204097</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5389620000000001</v>
+        <v>0.374239</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.411394</v>
+        <v>0.292415</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.639838</v>
+        <v>0.928462</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>0.024585</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.502993</v>
+        <v>0.18485</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.436465</v>
+        <v>0.375654</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.37517</v>
+        <v>0.183264</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.48186</v>
+        <v>0.3208</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.384046</v>
+        <v>0.291076</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.376423</v>
+        <v>0.197698</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.347181</v>
+        <v>0.177489</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.308314</v>
+        <v>0.177827</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.333457</v>
+        <v>0.198286</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.553759</v>
+        <v>0.5235379999999999</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.347069</v>
+        <v>0.204892</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.369131</v>
+        <v>0.189223</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.302611</v>
+        <v>0.230044</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.386076</v>
+        <v>0.301158</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.449874</v>
+        <v>0.423856</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.406115</v>
+        <v>0.181681</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.406321</v>
+        <v>0.280829</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0.976502</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.541739</v>
+        <v>0.404126</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.341506</v>
+        <v>0.193633</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.380249</v>
+        <v>0.345025</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.386049</v>
+        <v>0.290353</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.491512</v>
+        <v>0.464759</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.40828</v>
+        <v>0.320081</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.552604</v>
+        <v>0.596257</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2019,10 +2019,10 @@
         <v>0.337563</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.503861</v>
+        <v>0.37537</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0.024981</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.628294</v>
+        <v>0.338255</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.437713</v>
+        <v>0.290066</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.475156</v>
+        <v>0.283707</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.398069</v>
+        <v>0.279511</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.370569</v>
+        <v>0.156102</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.354769</v>
+        <v>0.181091</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.363717</v>
+        <v>0.148191</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0.001277</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.516505</v>
+        <v>0.19219</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.434196</v>
+        <v>0.331647</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.361777</v>
+        <v>0.248827</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4616</v>
+        <v>0.461685</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2535,10 +2535,10 @@
         <v>0.24894</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.475866</v>
+        <v>0.522045</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.468607</v>
+        <v>0.344788</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0.0089</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.504551</v>
+        <v>0.470502</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.580391</v>
+        <v>0.932761</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.427694</v>
+        <v>0.302454</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.471208</v>
+        <v>0.268012</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.482489</v>
+        <v>0.248463</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.415555</v>
+        <v>0.111857</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.497645</v>
+        <v>0.488619</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.427531</v>
+        <v>0.209422</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.547434</v>
+        <v>0.540313</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.423883</v>
+        <v>0.340335</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.609396</v>
+        <v>0.8961519999999999</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.458848</v>
+        <v>0.303552</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.577949</v>
+        <v>0.7186669999999999</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.480168</v>
+        <v>0.406277</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.458796</v>
+        <v>0.345689</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.465367</v>
+        <v>0.272954</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.468899</v>
+        <v>0.26815</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.485589</v>
+        <v>0.310176</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.459178</v>
+        <v>0.426154</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3438,10 +3438,10 @@
         <v>0.006629</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.510042</v>
+        <v>0.404336</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.452649</v>
+        <v>0.266412</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.466622</v>
+        <v>0.278417</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.478256</v>
+        <v>0.487593</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3610,10 +3610,10 @@
         <v>0.001254</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.514767</v>
+        <v>0.207468</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.459171</v>
+        <v>0.255236</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3696,10 +3696,10 @@
         <v>0.023631</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.612052</v>
+        <v>0.452147</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.749289</v>
+        <v>0.741973</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>0.07967</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.543894</v>
+        <v>0.374768</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3825,10 +3825,10 @@
         <v>0.00966</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.507545</v>
+        <v>0.368296</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.518267</v>
+        <v>0.5490159999999999</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.474849</v>
+        <v>0.298432</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.498379</v>
+        <v>0.446565</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.523181</v>
+        <v>0.603678</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.466956</v>
+        <v>0.318505</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.460705</v>
+        <v>0.25992</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.62104</v>
+        <v>0.568871</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.48091</v>
+        <v>0.187867</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.449841</v>
+        <v>0.254652</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6006629999999999</v>
+        <v>0.66025</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.460381</v>
+        <v>0.172915</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4341,10 +4341,10 @@
         <v>0.045998</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5039169999999999</v>
+        <v>0.266604</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.428547</v>
+        <v>0.129347</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.445821</v>
+        <v>0.184958</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.413876</v>
+        <v>0.324016</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4513,10 +4513,10 @@
         <v>1.5e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.506995</v>
+        <v>0.218279</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.515781</v>
+        <v>0.526626</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.463005</v>
+        <v>0.316534</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.54179</v>
+        <v>0.641736</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.623354</v>
+        <v>0.772266</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.467852</v>
+        <v>0.404186</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.616208</v>
+        <v>0.7786419999999999</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.558354</v>
+        <v>0.826611</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4857,10 +4857,10 @@
         <v>0.708865</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.5075229999999999</v>
+        <v>0.414174</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.478834</v>
+        <v>0.277559</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4943,10 +4943,10 @@
         <v>0.004367</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.5953850000000001</v>
+        <v>0.473658</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.432258</v>
+        <v>0.421349</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.368019</v>
+        <v>0.407656</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.870347</v>
+        <v>0.50058</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.494952</v>
+        <v>0.450453</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5158,10 +5158,10 @@
         <v>0.582001</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0.6655</v>
+        <v>0.458911</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.317021</v>
+        <v>0.405361</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.19303</v>
+        <v>0.377798</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.257831</v>
+        <v>0.430613</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.165248</v>
+        <v>0.397117</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.328451</v>
+        <v>0.423655</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.391037</v>
+        <v>0.404839</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.481873</v>
+        <v>0.464948</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.236983</v>
+        <v>0.393372</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5545,10 +5545,10 @@
         <v>0.6016089999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.592883</v>
+        <v>0.493869</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.380645</v>
+        <v>0.438555</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5631,10 +5631,10 @@
         <v>0.247725</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.530968</v>
+        <v>0.468633</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5674,10 +5674,10 @@
         <v>0.62088</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>0.678603</v>
+        <v>0.472043</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.614102</v>
+        <v>0.50002</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.401245</v>
+        <v>0.464834</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.450423</v>
+        <v>0.491177</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0.027839</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.528453</v>
+        <v>0.417531</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.304763</v>
+        <v>0.454454</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5932,10 +5932,10 @@
         <v>0.003416</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>0.481159</v>
+        <v>0.512112</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.667303</v>
+        <v>0.508081</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.301002</v>
+        <v>0.441626</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.2725</v>
+        <v>0.458106</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.474492</v>
+        <v>0.490084</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.456125</v>
+        <v>0.4279</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.495682</v>
+        <v>0.454205</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.315602</v>
+        <v>0.436612</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.3756</v>
+        <v>0.382103</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.464898</v>
+        <v>0.451362</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.345759</v>
+        <v>0.42379</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.453705</v>
+        <v>0.444654</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.340805</v>
+        <v>0.415102</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.596324</v>
+        <v>0.516859</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.289629</v>
+        <v>0.391061</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.288749</v>
+        <v>0.485686</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>0.041286</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.588858</v>
+        <v>0.494603</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.185138</v>
+        <v>0.463254</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6706,10 +6706,10 @@
         <v>0.00123</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.658005</v>
+        <v>0.422824</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6749,10 +6749,10 @@
         <v>0.202119</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.500278</v>
+        <v>0.44988</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.348544</v>
+        <v>0.425213</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6835,10 +6835,10 @@
         <v>0.525605</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.557254</v>
+        <v>0.444755</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.332137</v>
+        <v>0.436632</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6921,10 +6921,10 @@
         <v>0.08626300000000001</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.59172</v>
+        <v>0.49912</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.960938</v>
+        <v>0.563715</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.179031</v>
+        <v>0.389507</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>0.526569</v>
+        <v>0.506255</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7093,10 +7093,10 @@
         <v>0.001001</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G155" t="n">
-        <v>0.206722</v>
+        <v>0.501335</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.418214</v>
+        <v>0.456323</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.691951</v>
+        <v>0.553213</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.314972</v>
+        <v>0.462364</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.357447</v>
+        <v>0.453269</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0.50053</v>
+        <v>0.515413</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.213153</v>
+        <v>0.451902</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.184616</v>
+        <v>0.438799</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.206269</v>
+        <v>0.469295</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.545889</v>
+        <v>0.511132</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.272917</v>
+        <v>0.429074</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.668382</v>
+        <v>0.5357</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7609,10 +7609,10 @@
         <v>0.120908</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.604254</v>
+        <v>0.481434</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.611043</v>
+        <v>0.508425</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>0.552523</v>
+        <v>0.504507</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.263294</v>
+        <v>0.466723</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7781,10 +7781,10 @@
         <v>0.04874</v>
       </c>
       <c r="F171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.514923</v>
+        <v>0.482246</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.275304</v>
+        <v>0.456225</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>0.6921620000000001</v>
+        <v>0.515952</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.276554</v>
+        <v>0.442453</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.218449</v>
+        <v>0.421602</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.136369</v>
+        <v>0.444949</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.297321</v>
+        <v>0.450639</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.287513</v>
+        <v>0.454516</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.16663</v>
+        <v>0.432203</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.313554</v>
+        <v>0.447098</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.224525</v>
+        <v>0.416568</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.229023</v>
+        <v>0.453285</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.390085</v>
+        <v>0.495684</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.20579</v>
+        <v>0.413425</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.223675</v>
+        <v>0.429308</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.252287</v>
+        <v>0.434152</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.272466</v>
+        <v>0.459816</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.200198</v>
+        <v>0.470468</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.2149</v>
+        <v>0.404915</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.714043</v>
+        <v>0.536467</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8641,10 +8641,10 @@
         <v>0.030284</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.784598</v>
+        <v>0.468892</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0.631349</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.578097</v>
+        <v>0.492544</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.004122</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.716744</v>
+        <v>0.492719</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8770,10 +8770,10 @@
         <v>0.066251</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
-        <v>0.363107</v>
+        <v>0.53062</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.361021</v>
+        <v>0.44773</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.376544</v>
+        <v>0.481167</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.775739</v>
+        <v>0.565272</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8942,10 +8942,10 @@
         <v>0.054679</v>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>0.819833</v>
+        <v>0.486898</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.897996</v>
+        <v>0.570306</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -9028,10 +9028,10 @@
         <v>0.002745</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>0.285484</v>
+        <v>0.528224</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.431614</v>
+        <v>0.482716</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9114,10 +9114,10 @@
         <v>0.000426</v>
       </c>
       <c r="F202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.534492</v>
+        <v>0.295932</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0.484855</v>
+        <v>0.48925</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.466069</v>
+        <v>0.385223</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.425184</v>
+        <v>0.187561</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.500853</v>
+        <v>0.753292</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.466437</v>
+        <v>0.319672</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.477531</v>
+        <v>0.374675</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.46147</v>
+        <v>0.286753</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.534578</v>
+        <v>0.746277</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.455682</v>
+        <v>0.202876</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9544,10 +9544,10 @@
         <v>0.003103</v>
       </c>
       <c r="F212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.502169</v>
+        <v>0.460475</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9587,10 +9587,10 @@
         <v>0.021145</v>
       </c>
       <c r="F213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.542221</v>
+        <v>0.481156</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.45769</v>
+        <v>0.390334</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.456951</v>
+        <v>0.227712</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0.5445179999999999</v>
+        <v>0.517429</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.40367</v>
+        <v>0.166894</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0.076005</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.5119629999999999</v>
+        <v>0.301948</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9845,10 +9845,10 @@
         <v>0.0295</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.515761</v>
+        <v>0.422947</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.461035</v>
+        <v>0.313602</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.485625</v>
+        <v>0.336879</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9974,10 +9974,10 @@
         <v>0.015576</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0.543979</v>
+        <v>0.402455</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.4484</v>
+        <v>0.310298</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.439245</v>
+        <v>0.310456</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10103,10 +10103,10 @@
         <v>0.077533</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G225" t="n">
-        <v>0.484674</v>
+        <v>0.526801</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10146,10 +10146,10 @@
         <v>0.05967</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>0.467771</v>
+        <v>0.5000250000000001</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>0.518821</v>
+        <v>0.579475</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10232,10 +10232,10 @@
         <v>0.221442</v>
       </c>
       <c r="F228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.535266</v>
+        <v>0.46864</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.397091</v>
+        <v>0.302529</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.480487</v>
+        <v>0.289711</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10361,10 +10361,10 @@
         <v>0.056367</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.497299</v>
+        <v>0.523365</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.466311</v>
+        <v>0.466178</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10447,10 +10447,10 @@
         <v>0.025314</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.470872</v>
+        <v>0.726604</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.414428</v>
+        <v>0.220451</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.47587</v>
+        <v>0.326551</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.442201</v>
+        <v>0.407927</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.443692</v>
+        <v>0.279069</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.478356</v>
+        <v>0.255173</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.456214</v>
+        <v>0.289688</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.453077</v>
+        <v>0.263423</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.474608</v>
+        <v>0.403605</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.459362</v>
+        <v>0.336951</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="G243" t="n">
-        <v>0.559408</v>
+        <v>0.508341</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>0.566335</v>
+        <v>0.566155</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.594759</v>
+        <v>0.51834</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.601839</v>
+        <v>0.930541</v>
       </c>
       <c r="H246" t="n">
         <v>1</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.605868</v>
+        <v>0.960212</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
@@ -11092,10 +11092,10 @@
         <v>0.575419</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.490543</v>
+        <v>0.776861</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.623403</v>
+        <v>0.967729</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.446568</v>
+        <v>0.349249</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.42819</v>
+        <v>0.178017</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.5007509999999999</v>
+        <v>0.639827</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.411467</v>
+        <v>0.142258</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.494796</v>
+        <v>0.307092</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         <v>0.0002</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.505405</v>
+        <v>0.339766</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11436,10 +11436,10 @@
         <v>0.080472</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.480564</v>
+        <v>0.740532</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11479,10 +11479,10 @@
         <v>0.326965</v>
       </c>
       <c r="F257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.49569</v>
+        <v>0.673318</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.557913</v>
+        <v>0.928011</v>
       </c>
       <c r="H258" t="n">
         <v>1</v>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>0.472347</v>
+        <v>0.315291</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.444892</v>
+        <v>0.164375</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.449633</v>
+        <v>0.303397</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.517241</v>
+        <v>0.545346</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.438378</v>
+        <v>0.409793</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11780,10 +11780,10 @@
         <v>0.575442</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.478858</v>
+        <v>0.644274</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11823,10 +11823,10 @@
         <v>0.0009479999999999999</v>
       </c>
       <c r="F265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.502463</v>
+        <v>0.415836</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.423331</v>
+        <v>0.163741</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11909,10 +11909,10 @@
         <v>0.0305</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.45027</v>
+        <v>0.51476</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="G268" t="n">
-        <v>0.43217</v>
+        <v>0.263592</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.467692</v>
+        <v>0.285024</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.483622</v>
+        <v>0.461411</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.450108</v>
+        <v>0.273214</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.463998</v>
+        <v>0.402654</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.44728</v>
+        <v>0.359687</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12210,10 +12210,10 @@
         <v>0.010022</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.434771</v>
+        <v>0.700528</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12253,10 +12253,10 @@
         <v>0.09322999999999999</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.57681</v>
+        <v>0.32752</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0.492856</v>
+        <v>0.484742</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.498104</v>
+        <v>0.44605</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.431734</v>
+        <v>0.256617</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.467495</v>
+        <v>0.343334</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.453726</v>
+        <v>0.266162</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.468967</v>
+        <v>0.238404</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.4726</v>
+        <v>0.20644</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.450019</v>
+        <v>0.233663</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12640,10 +12640,10 @@
         <v>0.036524</v>
       </c>
       <c r="F284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.528715</v>
+        <v>0.328399</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>0.005798</v>
       </c>
       <c r="F285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.520227</v>
+        <v>0.446348</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12726,10 +12726,10 @@
         <v>0.011748</v>
       </c>
       <c r="F286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G286" t="n">
-        <v>0.479268</v>
+        <v>0.606676</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0.377228</v>
+        <v>0.445915</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12812,10 +12812,10 @@
         <v>0.03449</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.514601</v>
+        <v>0.434626</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12855,10 +12855,10 @@
         <v>0.007314</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
-        <v>0.45718</v>
+        <v>0.543343</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.459257</v>
+        <v>0.269032</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12941,10 +12941,10 @@
         <v>0.970367</v>
       </c>
       <c r="F291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.53545</v>
+        <v>0.437968</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.4518</v>
+        <v>0.306504</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13027,10 +13027,10 @@
         <v>0.018485</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.581943</v>
+        <v>0.393189</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.475398</v>
+        <v>0.235303</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.49355</v>
+        <v>0.333653</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.585395</v>
+        <v>0.977164</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.44279</v>
+        <v>0.375946</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.481614</v>
+        <v>0.196397</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.474093</v>
+        <v>0.359614</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13328,10 +13328,10 @@
         <v>0.003759</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.508888</v>
+        <v>0.347757</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.4525</v>
+        <v>0.085178</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0.5038010000000001</v>
+        <v>0.514508</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13457,10 +13457,10 @@
         <v>0.921582</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.453796</v>
+        <v>0.703254</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -13500,10 +13500,10 @@
         <v>0.798277</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.498298</v>
+        <v>0.733312</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13543,10 +13543,10 @@
         <v>0.018456</v>
       </c>
       <c r="F305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.516379</v>
+        <v>0.261168</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13586,10 +13586,10 @@
         <v>0.259924</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.503208</v>
+        <v>0.49759</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13629,10 +13629,10 @@
         <v>0.272612</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>0.439652</v>
+        <v>0.525972</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.468409</v>
+        <v>0.37304</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13715,10 +13715,10 @@
         <v>0.015311</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.476839</v>
+        <v>0.608022</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.479561</v>
+        <v>0.23204</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13801,10 +13801,10 @@
         <v>0.227849</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.508572</v>
+        <v>0.498429</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.46254</v>
+        <v>0.170386</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.484153</v>
+        <v>0.469485</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.485498</v>
+        <v>0.223622</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.16415</v>
+        <v>0.199937</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.297166</v>
+        <v>0.232719</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.369899</v>
+        <v>0.311444</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.768319</v>
+        <v>0.595451</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.411457</v>
+        <v>0.256262</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.95221</v>
+        <v>0.971333</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.242376</v>
+        <v>0.199073</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.431377</v>
+        <v>0.339194</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.228267</v>
+        <v>0.193566</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.268923</v>
+        <v>0.175226</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.332127</v>
+        <v>0.376223</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.413078</v>
+        <v>0.353347</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14489,10 +14489,10 @@
         <v>0.025862</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.56185</v>
+        <v>0.356557</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.823052</v>
+        <v>0.548437</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.358861</v>
+        <v>0.46204</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="G330" t="n">
-        <v>0.694816</v>
+        <v>0.565287</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.767042</v>
+        <v>0.752447</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.36951</v>
+        <v>0.382842</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.993181</v>
+        <v>0.965707</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.477079</v>
+        <v>0.398733</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.458469</v>
+        <v>0.299611</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.315656</v>
+        <v>0.335686</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.224562</v>
+        <v>0.186135</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.219694</v>
+        <v>0.325471</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.364229</v>
+        <v>0.24625</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15048,10 +15048,10 @@
         <v>0.01392</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.5614209999999999</v>
+        <v>0.472174</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.365122</v>
+        <v>0.326271</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.30768</v>
+        <v>0.2988</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.221735</v>
+        <v>0.140519</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.369167</v>
+        <v>0.338135</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.255369</v>
+        <v>0.238528</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.384876</v>
+        <v>0.291748</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15349,10 +15349,10 @@
         <v>9.899999999999999e-05</v>
       </c>
       <c r="F347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.598608</v>
+        <v>0.308848</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.380928</v>
+        <v>0.341868</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -15438,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>0.934767</v>
+        <v>0.861117</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.570286</v>
+        <v>0.740178</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.313128</v>
+        <v>0.311997</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.249659</v>
+        <v>0.298975</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.149413</v>
+        <v>0.075256</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.109662</v>
+        <v>0.073888</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.164409</v>
+        <v>0.186814</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.426124</v>
+        <v>0.264173</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.154889</v>
+        <v>0.230247</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.350596</v>
+        <v>0.428798</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.087713</v>
+        <v>0.159389</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15908,10 +15908,10 @@
         <v>1e-06</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.154956</v>
+        <v>0.598279</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.405728</v>
+        <v>0.24625</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0.348347</v>
+        <v>0.383954</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.269711</v>
+        <v>0.360678</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16080,10 +16080,10 @@
         <v>0.594795</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0.609493</v>
+        <v>0.481766</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.212526</v>
+        <v>0.147922</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.275208</v>
+        <v>0.249459</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.379111</v>
+        <v>0.287585</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.320502</v>
+        <v>0.249305</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.23417</v>
+        <v>0.229047</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.293359</v>
+        <v>0.367427</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.325066</v>
+        <v>0.306975</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.271637</v>
+        <v>0.19932</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.360166</v>
+        <v>0.215355</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16510,10 +16510,10 @@
         <v>0.13931</v>
       </c>
       <c r="F374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5136579999999999</v>
+        <v>0.448763</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.370713</v>
+        <v>0.345172</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>0.837448</v>
+        <v>0.595506</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.162515</v>
+        <v>0.193208</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.370139</v>
+        <v>0.348222</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.370443</v>
+        <v>0.277708</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.39972</v>
+        <v>0.137559</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.297319</v>
+        <v>0.031451</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16854,10 +16854,10 @@
         <v>0.248686</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.539592</v>
+        <v>0.230456</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.201841</v>
+        <v>0.247738</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.365957</v>
+        <v>0.397813</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.172361</v>
+        <v>0.204104</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.219303</v>
+        <v>0.219074</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.274237</v>
+        <v>0.248945</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.290391</v>
+        <v>0.240884</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.163844</v>
+        <v>0.17695</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.154356</v>
+        <v>0.141807</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.375051</v>
+        <v>0.275365</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.468726</v>
+        <v>0.385988</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.77061</v>
+        <v>0.796467</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.245181</v>
+        <v>0.174174</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.6850619999999999</v>
+        <v>0.750518</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.44829</v>
+        <v>0.350313</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17499,10 +17499,10 @@
         <v>0.000479</v>
       </c>
       <c r="F397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.6295190000000001</v>
+        <v>0.47827</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.320787</v>
+        <v>0.238504</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.272418</v>
+        <v>0.239819</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17628,10 +17628,10 @@
         <v>0.029817</v>
       </c>
       <c r="F400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.500927</v>
+        <v>0.497047</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17671,10 +17671,10 @@
         <v>0.427139</v>
       </c>
       <c r="F401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.587018</v>
+        <v>0.475093</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.215253</v>
+        <v>0.243108</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.834212</v>
+        <v>0.644108</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.455951</v>
+        <v>0.35434</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.370896</v>
+        <v>0.318385</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.33034</v>
+        <v>0.261584</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0.277667</v>
+        <v>0.280984</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.663313</v>
+        <v>0.616773</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.218834</v>
+        <v>0.157629</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.301025</v>
+        <v>0.251542</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.586933</v>
+        <v>0.820673</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.260789</v>
+        <v>0.190505</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.249173</v>
+        <v>0.207553</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.9995309999999999</v>
+        <v>0.999134</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
